--- a/artfynd/A 6605-2025 artfynd.xlsx
+++ b/artfynd/A 6605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122600011</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6605-2025 artfynd.xlsx
+++ b/artfynd/A 6605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122600011</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6605-2025 artfynd.xlsx
+++ b/artfynd/A 6605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122600011</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6605-2025 artfynd.xlsx
+++ b/artfynd/A 6605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122600011</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6605-2025 artfynd.xlsx
+++ b/artfynd/A 6605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122600011</v>
       </c>
       <c r="B2" t="n">
-        <v>92221</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6605-2025 artfynd.xlsx
+++ b/artfynd/A 6605-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122600011</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
